--- a/Result/profitability/3354.xlsx
+++ b/Result/profitability/3354.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>-0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.23125</v>
+        <v>-0.2175</v>
       </c>
       <c r="N2" t="n">
-        <v>13.395</v>
+        <v>17.1325</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,16 +780,16 @@
         <v>0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1825</v>
+        <v>-0.19875</v>
       </c>
       <c r="N3" t="n">
-        <v>14.65</v>
+        <v>17.69</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03500000000000003</v>
+        <v>-0.03</v>
       </c>
       <c r="N4" t="n">
-        <v>17.22625</v>
+        <v>20.0325</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -914,13 +914,13 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03375000000000003</v>
+        <v>0.01874999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>17.19375</v>
+        <v>20.915</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01249999999999998</v>
+        <v>0.002499999999999988</v>
       </c>
       <c r="N6" t="n">
-        <v>16.36625</v>
+        <v>19.3325</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003749999999999976</v>
+        <v>0.006249999999999988</v>
       </c>
       <c r="N7" t="n">
-        <v>16.71125</v>
+        <v>18.76</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02374999999999998</v>
+        <v>0.03124999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>16.6975</v>
+        <v>17.47</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.4</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.005000000000000025</v>
+        <v>-0.005000000000000011</v>
       </c>
       <c r="N9" t="n">
         <v>13.3</v>
@@ -1899,7 +1899,7 @@
         <v>0.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04124999999999997</v>
+        <v>0.04125</v>
       </c>
       <c r="N12" t="n">
         <v>13.9375</v>
@@ -2026,7 +2026,7 @@
         <v>0.21</v>
       </c>
       <c r="M13" t="n">
-        <v>0.08499999999999996</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>14.91375</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3354</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>37</v>
+      </c>
+      <c r="D75" t="n">
+        <v>24</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-32.12%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.165</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.2675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3529411764705883</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2117888965044552</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7924528301886793</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>5.325581395348837</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
